--- a/Config/MiniTemplate/Datas/Config/__enums__.xlsx
+++ b/Config/MiniTemplate/Datas/Config/__enums__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
   <si>
     <t>##var</t>
   </si>
@@ -86,45 +86,6 @@
     <t>注释</t>
   </si>
   <si>
-    <t>EQuality</t>
-  </si>
-  <si>
-    <t>WHITE</t>
-  </si>
-  <si>
-    <t>白</t>
-  </si>
-  <si>
-    <t>最差品质</t>
-  </si>
-  <si>
-    <t>BLUE</t>
-  </si>
-  <si>
-    <t>蓝</t>
-  </si>
-  <si>
-    <t>蓝色的</t>
-  </si>
-  <si>
-    <t>PURPLE</t>
-  </si>
-  <si>
-    <t>紫</t>
-  </si>
-  <si>
-    <t>紫色的</t>
-  </si>
-  <si>
-    <t>RED</t>
-  </si>
-  <si>
-    <t>红</t>
-  </si>
-  <si>
-    <t>最高品质</t>
-  </si>
-  <si>
     <t>test.AccessFlag</t>
   </si>
   <si>
@@ -147,6 +108,21 @@
   </si>
   <si>
     <t>位标记使用示例</t>
+  </si>
+  <si>
+    <t>RedDotType</t>
+  </si>
+  <si>
+    <t>Main</t>
+  </si>
+  <si>
+    <t>根节点红点</t>
+  </si>
+  <si>
+    <t>RedDotTest</t>
+  </si>
+  <si>
+    <t>测试红点</t>
   </si>
 </sst>
 </file>
@@ -1109,7 +1085,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -1209,12 +1185,12 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:11">
+    <row r="4" spans="2:10">
       <c r="B4" t="s">
         <v>19</v>
       </c>
       <c r="C4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
@@ -1222,108 +1198,76 @@
       <c r="H4" t="s">
         <v>20</v>
       </c>
-      <c r="I4" t="s">
-        <v>21</v>
-      </c>
       <c r="J4">
         <v>1</v>
       </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
     </row>
-    <row r="5" spans="8:11">
+    <row r="5" spans="8:10">
       <c r="H5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J5">
         <v>2</v>
       </c>
-      <c r="K5" t="s">
+    </row>
+    <row r="6" spans="8:10">
+      <c r="H6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="8:10">
+      <c r="H7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="8:11">
+      <c r="H8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" t="s">
         <v>25</v>
       </c>
+      <c r="K8" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="6" spans="8:11">
-      <c r="H6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" t="s">
+    <row r="9" spans="2:11">
+      <c r="B9" t="s">
         <v>27</v>
       </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="C9" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="s">
         <v>28</v>
       </c>
+      <c r="I9"/>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="7" spans="8:11">
-      <c r="H7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I7" t="s">
+    <row r="10" spans="8:11">
+      <c r="H10" t="s">
         <v>30</v>
       </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="I10"/>
+      <c r="J10">
+        <v>2</v>
+      </c>
+      <c r="K10" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10">
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" t="b">
-        <v>1</v>
-      </c>
-      <c r="D8" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="8:10">
-      <c r="H9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="8:10">
-      <c r="H10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="8:10">
-      <c r="H11" t="s">
-        <v>36</v>
-      </c>
-      <c r="J11">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="8:11">
-      <c r="H12" t="s">
-        <v>37</v>
-      </c>
-      <c r="J12" t="s">
-        <v>38</v>
-      </c>
-      <c r="K12" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/Config/MiniTemplate/Datas/Config/__enums__.xlsx
+++ b/Config/MiniTemplate/Datas/Config/__enums__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="37">
   <si>
     <t>##var</t>
   </si>
@@ -113,16 +113,31 @@
     <t>RedDotType</t>
   </si>
   <si>
-    <t>Main</t>
+    <t>Root</t>
   </si>
   <si>
     <t>根节点红点</t>
   </si>
   <si>
-    <t>RedDotTest</t>
-  </si>
-  <si>
-    <t>测试红点</t>
+    <t>RedDotTest1</t>
+  </si>
+  <si>
+    <t>测试红点1</t>
+  </si>
+  <si>
+    <t>RedDotTest2</t>
+  </si>
+  <si>
+    <t>测试红点2</t>
+  </si>
+  <si>
+    <t>RedDotTestChild1</t>
+  </si>
+  <si>
+    <t>测试红点子节点</t>
+  </si>
+  <si>
+    <t>RedDotTestChild2</t>
   </si>
 </sst>
 </file>
@@ -1085,7 +1100,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -1250,7 +1265,6 @@
       <c r="H9" t="s">
         <v>28</v>
       </c>
-      <c r="I9"/>
       <c r="J9">
         <v>1</v>
       </c>
@@ -1262,12 +1276,44 @@
       <c r="H10" t="s">
         <v>30</v>
       </c>
-      <c r="I10"/>
       <c r="J10">
         <v>2</v>
       </c>
       <c r="K10" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="8:11">
+      <c r="H11" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11">
+        <v>3</v>
+      </c>
+      <c r="K11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="8:11">
+      <c r="H12" t="s">
+        <v>34</v>
+      </c>
+      <c r="J12">
+        <v>4</v>
+      </c>
+      <c r="K12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="8:11">
+      <c r="H13" t="s">
+        <v>36</v>
+      </c>
+      <c r="J13">
+        <v>5</v>
+      </c>
+      <c r="K13" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
